--- a/Plantilla excel.xlsx
+++ b/Plantilla excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d005370dc6139bf9/Escritorio/Proyectos/SistemaWebPedidosBack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{A2AEC496-F57F-4A12-8436-1754304AE94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F0C96A-C845-4A12-B820-9EE3C449FBA6}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{A2AEC496-F57F-4A12-8436-1754304AE94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63A99D14-3074-4496-B5AC-C34682359F53}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21090" xr2:uid="{EC0B353E-FCF1-4788-B064-5D537B3BC33A}"/>
   </bookViews>
@@ -169,7 +169,7 @@
     <t>Girado a:</t>
   </si>
   <si>
-    <t xml:space="preserve">	CHEMIFABRIK PERU SOCIEDAD ANONIMA CERRADA - CHEMIFABRIK</t>
+    <t>awdawd</t>
   </si>
 </sst>
 </file>
@@ -518,15 +518,79 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -536,21 +600,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -562,61 +617,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -999,6 +999,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -1318,54 +1322,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="25" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25" t="s">
+      <c r="E2" s="24"/>
+      <c r="F2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25" t="s">
+      <c r="G2" s="24"/>
+      <c r="H2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25" t="s">
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25" t="s">
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="25"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1384,190 +1388,190 @@
       <c r="M3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="23" t="s">
+      <c r="A5" s="51"/>
+      <c r="B5" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
     </row>
     <row r="6" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="29" t="s">
+      <c r="A7" s="51"/>
+      <c r="B7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
     </row>
     <row r="8" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
-      <c r="B8" s="47" t="s">
+      <c r="A8" s="51"/>
+      <c r="B8" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="45" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="46"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="23"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="50"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="28"/>
       <c r="J9" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="42" t="s">
+      <c r="L9" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
       <c r="O9" s="18" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="44"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="38"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
       <c r="O10" s="1"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
+      <c r="A11" s="51"/>
       <c r="B11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="36" t="s">
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="38"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="31"/>
     </row>
     <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="11"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="39" t="s">
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="40"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="41"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="34"/>
     </row>
     <row r="13" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="10" t="s">
         <v>18</v>
       </c>
@@ -1586,7 +1590,7 @@
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="32"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="11"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -1596,14 +1600,14 @@
       <c r="H14" s="14"/>
       <c r="I14" s="15"/>
       <c r="J14" s="11"/>
-      <c r="L14" s="27" t="s">
+      <c r="L14" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="47"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="32"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="6" t="s">
         <v>19</v>
       </c>
@@ -1615,16 +1619,16 @@
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
       <c r="I15" s="15"/>
-      <c r="J15" s="28" t="s">
+      <c r="J15" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="6" t="s">
         <v>15</v>
       </c>
@@ -1641,7 +1645,7 @@
       <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="8"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1658,44 +1662,30 @@
       <c r="O17" s="9"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
     </row>
     <row r="21" spans="1:15" ht="52.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
     </row>
     <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B7:O7"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J11:O11"/>
-    <mergeCell ref="J12:O12"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="J1:O1"/>
     <mergeCell ref="B26:D28"/>
@@ -1712,6 +1702,20 @@
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A2:A17"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J11:O11"/>
+    <mergeCell ref="J12:O12"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="B7:O7"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="C8:I8"/>
   </mergeCells>
   <pageMargins left="0.12" right="0.12" top="0.3" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
